--- a/ig/main/ValueSet-jdv-antecedent-obstetrical-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-antecedent-obstetrical-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250606103858</t>
+    <t>20250611134353</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-06T10:38:58+01:00</t>
+    <t>2025-06-11T13:43:53+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-antecedent-obstetrical-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-antecedent-obstetrical-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250611134353</t>
+    <t>20250616134740</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-11T13:43:53+01:00</t>
+    <t>2025-06-16T13:47:40+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-antecedent-obstetrical-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-antecedent-obstetrical-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250616134740</t>
+    <t>20250624152100</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-16T13:47:40+01:00</t>
+    <t>2025-06-24T15:21:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-antecedent-obstetrical-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-antecedent-obstetrical-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250624152100</t>
+    <t>20251216141839</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24T15:21:00+01:00</t>
+    <t>2025-12-16T14:18:39+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -137,7 +137,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/terminologie-cim-10</t>
+    <t>http://hl7.org/fhir/sid/icd-10</t>
   </si>
   <si>
     <t>MED-1184</t>

--- a/ig/main/ValueSet-jdv-antecedent-obstetrical-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-antecedent-obstetrical-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251216141839</t>
+    <t>20260220142105</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T14:18:39+01:00</t>
+    <t>2026-02-20T14:21:05+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-antecedent-obstetrical-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-antecedent-obstetrical-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260220142105</t>
+    <t>20260311144904</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T14:21:05+01:00</t>
+    <t>2026-03-11T14:49:04+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-antecedent-obstetrical-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-antecedent-obstetrical-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260311144904</t>
+    <t>20260420150251</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T14:49:04+01:00</t>
+    <t>2026-04-20T15:02:51+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-antecedent-obstetrical-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-antecedent-obstetrical-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260420150251</t>
+    <t>20260619134043</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:02:51+01:00</t>
+    <t>2026-06-19T13:40:43+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
